--- a/pokemon-card-tsuyosa-template.xlsx
+++ b/pokemon-card-tsuyosa-template.xlsx
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>ひふきトカゲ</t>
+          <t>ばくえんリュウ</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -1086,26 +1086,26 @@
         </is>
       </c>
       <c r="D2" s="13" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>ひのこ</t>
+          <t>ひのたま</t>
         </is>
       </c>
       <c r="F2" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>ほのおのしっぽ</t>
+          <t>だいもんじ</t>
         </is>
       </c>
       <c r="I2" s="13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J2" s="13" t="n">
         <v>2</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>あめふりガエル</t>
+          <t>あらしクジラ</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -1144,11 +1144,11 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>みずでっぽう</t>
+          <t>みずしぶき</t>
         </is>
       </c>
       <c r="F3" s="13" t="n">
@@ -1159,11 +1159,11 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>ずぶぬれ</t>
+          <t>だいこうずい</t>
         </is>
       </c>
       <c r="I3" s="13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J3" s="13" t="n">
         <v>2</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>はっぱウサギ</t>
+          <t>ひふきトカゲ</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>くさ</t>
+          <t>ほのお</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>はっぱカッター</t>
+          <t>ひのこ</t>
         </is>
       </c>
       <c r="F4" s="13" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>ふわタックル</t>
+          <t>ほのおのしっぽ</t>
         </is>
       </c>
       <c r="I4" s="13" t="n">
@@ -1249,17 +1249,47 @@
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>あめふりガエル</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>みず</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>みずでっぽう</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>ずぶぬれ</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" s="14">
         <f>IF(D5="","",ROUND(D5/設定!$B$3+MAX(F5,I5)/設定!$B$4+L5,1))</f>
         <v/>
@@ -1277,17 +1307,47 @@
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>はっぱウサギ</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>くさ</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>はっぱカッター</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>ふわタックル</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" s="14">
         <f>IF(D6="","",ROUND(D6/設定!$B$3+MAX(F6,I6)/設定!$B$4+L6,1))</f>
         <v/>
@@ -1305,17 +1365,47 @@
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>ちびキツネ</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>ほのお</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>ぽっぽひ</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>ほのおダッシュ</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" s="14">
         <f>IF(D7="","",ROUND(D7/設定!$B$3+MAX(F7,I7)/設定!$B$4+L7,1))</f>
         <v/>
@@ -1333,17 +1423,47 @@
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>ちびカメ</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>みず</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>あわ</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>ころころタックル</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" s="14">
         <f>IF(D8="","",ROUND(D8/設定!$B$3+MAX(F8,I8)/設定!$B$4+L8,1))</f>
         <v/>
@@ -1361,17 +1481,47 @@
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="13" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>きのこぼうず</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>くさ</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>ぽふぽふ</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>ほうしこうげき</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" s="14">
         <f>IF(D9="","",ROUND(D9/設定!$B$3+MAX(F9,I9)/設定!$B$4+L9,1))</f>
         <v/>
@@ -1389,17 +1539,47 @@
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="13" t="n"/>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>ひまわりヒヨコ</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>くさ</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>つつく</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>ひかりのたね</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" s="14">
         <f>IF(D10="","",ROUND(D10/設定!$B$3+MAX(F10,I10)/設定!$B$4+L10,1))</f>
         <v/>
@@ -2424,25 +2604,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J2" s="16">
         <f>SUMPRODUCT(COUNTIF($B2:$I2,カード一覧!$A$2:$A$41)*(カード一覧!$N$2:$N$41="A"))</f>
